--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121107425</v>
+        <v>121108045</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687373</v>
+        <v>687312</v>
       </c>
       <c r="R2" t="n">
-        <v>6619807</v>
+        <v>6619846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108045</v>
+        <v>121107620</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687312</v>
+        <v>687383</v>
       </c>
       <c r="R3" t="n">
-        <v>6619846</v>
+        <v>6619778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121107440</v>
+        <v>121108150</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>105186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +904,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687379</v>
+        <v>687313</v>
       </c>
       <c r="R4" t="n">
-        <v>6619807</v>
+        <v>6619866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107537</v>
+        <v>121107425</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,47 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687377</v>
+        <v>687373</v>
       </c>
       <c r="R5" t="n">
-        <v>6619797</v>
+        <v>6619807</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107620</v>
+        <v>121107440</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>79219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,42 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687383</v>
+        <v>687379</v>
       </c>
       <c r="R7" t="n">
-        <v>6619778</v>
+        <v>6619807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107965</v>
+        <v>121107537</v>
       </c>
       <c r="B8" t="n">
-        <v>57364</v>
+        <v>8432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,43 +1339,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687312</v>
+        <v>687377</v>
       </c>
       <c r="R8" t="n">
-        <v>6619814</v>
+        <v>6619797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,6 +1420,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121108150</v>
+        <v>121108047</v>
       </c>
       <c r="B9" t="n">
-        <v>105176</v>
+        <v>92008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,54 +1451,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687313</v>
+        <v>687309</v>
       </c>
       <c r="R9" t="n">
-        <v>6619866</v>
+        <v>6619846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1523,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1546,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121108047</v>
+        <v>121107965</v>
       </c>
       <c r="B10" t="n">
-        <v>91998</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687309</v>
+        <v>687312</v>
       </c>
       <c r="R10" t="n">
-        <v>6619846</v>
+        <v>6619814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
         <v>121107530</v>
       </c>
       <c r="B11" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108045</v>
+        <v>121108047</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687312</v>
+        <v>687309</v>
       </c>
       <c r="R2" t="n">
         <v>6619846</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108150</v>
+        <v>121108045</v>
       </c>
       <c r="B4" t="n">
-        <v>105186</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,54 +899,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687313</v>
+        <v>687312</v>
       </c>
       <c r="R4" t="n">
-        <v>6619866</v>
+        <v>6619846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107425</v>
+        <v>121107537</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1006,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687373</v>
+        <v>687377</v>
       </c>
       <c r="R5" t="n">
-        <v>6619807</v>
+        <v>6619797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1118,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107967</v>
+        <v>121107440</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,43 +1118,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687303</v>
+        <v>687379</v>
       </c>
       <c r="R6" t="n">
-        <v>6619820</v>
+        <v>6619807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107440</v>
+        <v>121107965</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1224,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687379</v>
+        <v>687312</v>
       </c>
       <c r="R7" t="n">
-        <v>6619807</v>
+        <v>6619814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107537</v>
+        <v>121107967</v>
       </c>
       <c r="B8" t="n">
         <v>8432</v>
@@ -1361,25 +1349,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687377</v>
+        <v>687303</v>
       </c>
       <c r="R8" t="n">
-        <v>6619797</v>
+        <v>6619820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1404,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1439,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121108047</v>
+        <v>121108150</v>
       </c>
       <c r="B9" t="n">
-        <v>92008</v>
+        <v>105186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,38 +1434,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687309</v>
+        <v>687313</v>
       </c>
       <c r="R9" t="n">
-        <v>6619846</v>
+        <v>6619866</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,6 +1522,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107965</v>
+        <v>121107425</v>
       </c>
       <c r="B10" t="n">
         <v>57367</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687312</v>
+        <v>687373</v>
       </c>
       <c r="R10" t="n">
-        <v>6619814</v>
+        <v>6619807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107440</v>
+        <v>121107965</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,34 +1122,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687379</v>
+        <v>687312</v>
       </c>
       <c r="R6" t="n">
-        <v>6619807</v>
+        <v>6619814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107965</v>
+        <v>121107967</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,31 +1225,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687312</v>
+        <v>687303</v>
       </c>
       <c r="R7" t="n">
-        <v>6619814</v>
+        <v>6619820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107967</v>
+        <v>121107440</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,43 +1332,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687303</v>
+        <v>687379</v>
       </c>
       <c r="R8" t="n">
-        <v>6619820</v>
+        <v>6619807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108047</v>
+        <v>121108045</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687309</v>
+        <v>687312</v>
       </c>
       <c r="R2" t="n">
         <v>6619846</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108045</v>
+        <v>121107440</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,39 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687312</v>
+        <v>687379</v>
       </c>
       <c r="R4" t="n">
-        <v>6619846</v>
+        <v>6619807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107965</v>
+        <v>121108150</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>105199</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,43 +1118,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687312</v>
+        <v>687313</v>
       </c>
       <c r="R6" t="n">
-        <v>6619814</v>
+        <v>6619866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1206,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107440</v>
+        <v>121107965</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,34 +1348,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687379</v>
+        <v>687312</v>
       </c>
       <c r="R8" t="n">
-        <v>6619807</v>
+        <v>6619814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121108150</v>
+        <v>121107425</v>
       </c>
       <c r="B9" t="n">
-        <v>105186</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,54 +1451,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687313</v>
+        <v>687373</v>
       </c>
       <c r="R9" t="n">
-        <v>6619866</v>
+        <v>6619807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1528,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107425</v>
+        <v>121108047</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>92020</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,39 +1562,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687373</v>
+        <v>687309</v>
       </c>
       <c r="R10" t="n">
-        <v>6619807</v>
+        <v>6619846</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
         <v>121107530</v>
       </c>
       <c r="B11" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121107620</v>
+        <v>121107440</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687383</v>
+        <v>687379</v>
       </c>
       <c r="R3" t="n">
-        <v>6619778</v>
+        <v>6619807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121107440</v>
+        <v>121107967</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +896,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687379</v>
+        <v>687303</v>
       </c>
       <c r="R4" t="n">
-        <v>6619807</v>
+        <v>6619820</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1106,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121108150</v>
+        <v>121108047</v>
       </c>
       <c r="B6" t="n">
-        <v>105199</v>
+        <v>92021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,54 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687313</v>
+        <v>687309</v>
       </c>
       <c r="R6" t="n">
-        <v>6619866</v>
+        <v>6619846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107967</v>
+        <v>121107425</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,31 +1217,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1270,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687303</v>
+        <v>687373</v>
       </c>
       <c r="R7" t="n">
-        <v>6619820</v>
+        <v>6619807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107965</v>
+        <v>121107620</v>
       </c>
       <c r="B8" t="n">
         <v>57367</v>
@@ -1366,21 +1346,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687312</v>
+        <v>687383</v>
       </c>
       <c r="R8" t="n">
-        <v>6619814</v>
+        <v>6619778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107425</v>
+        <v>121107965</v>
       </c>
       <c r="B9" t="n">
         <v>57367</v>
@@ -1484,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687373</v>
+        <v>687312</v>
       </c>
       <c r="R9" t="n">
-        <v>6619807</v>
+        <v>6619814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121108047</v>
+        <v>121108150</v>
       </c>
       <c r="B10" t="n">
-        <v>92020</v>
+        <v>105200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,38 +1541,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687309</v>
+        <v>687313</v>
       </c>
       <c r="R10" t="n">
-        <v>6619846</v>
+        <v>6619866</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,6 +1629,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>121107530</v>
       </c>
       <c r="B11" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108045</v>
+        <v>121108047</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687312</v>
+        <v>687309</v>
       </c>
       <c r="R2" t="n">
         <v>6619846</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121107440</v>
+        <v>121108045</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687379</v>
+        <v>687312</v>
       </c>
       <c r="R3" t="n">
-        <v>6619807</v>
+        <v>6619846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121107967</v>
+        <v>121107440</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687303</v>
+        <v>687379</v>
       </c>
       <c r="R4" t="n">
-        <v>6619820</v>
+        <v>6619807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107537</v>
+        <v>121107425</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,47 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687377</v>
+        <v>687373</v>
       </c>
       <c r="R5" t="n">
-        <v>6619797</v>
+        <v>6619807</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1075,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121108047</v>
+        <v>121108150</v>
       </c>
       <c r="B6" t="n">
-        <v>92021</v>
+        <v>105203</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1105,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687309</v>
+        <v>687313</v>
       </c>
       <c r="R6" t="n">
-        <v>6619846</v>
+        <v>6619866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1193,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107425</v>
+        <v>121107967</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>8435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,31 +1224,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687373</v>
+        <v>687303</v>
       </c>
       <c r="R7" t="n">
-        <v>6619807</v>
+        <v>6619820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107620</v>
+        <v>121107537</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>8435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,33 +1331,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1360,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687383</v>
+        <v>687377</v>
       </c>
       <c r="R8" t="n">
-        <v>6619778</v>
+        <v>6619797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,6 +1412,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,7 +1434,7 @@
         <v>121107965</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121108150</v>
+        <v>121107620</v>
       </c>
       <c r="B10" t="n">
-        <v>105200</v>
+        <v>57370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,43 +1550,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1585,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687313</v>
+        <v>687383</v>
       </c>
       <c r="R10" t="n">
-        <v>6619866</v>
+        <v>6619778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1630,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>121107530</v>
       </c>
       <c r="B11" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45221-2024 artfynd.xlsx
+++ b/artfynd/A 45221-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108047</v>
+        <v>121107620</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687309</v>
+        <v>687383</v>
       </c>
       <c r="R2" t="n">
-        <v>6619846</v>
+        <v>6619778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108045</v>
+        <v>121107965</v>
       </c>
       <c r="B3" t="n">
         <v>57370</v>
@@ -813,7 +821,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,7 +833,7 @@
         <v>687312</v>
       </c>
       <c r="R3" t="n">
-        <v>6619846</v>
+        <v>6619814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121107440</v>
+        <v>121108150</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>105203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +904,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687379</v>
+        <v>687313</v>
       </c>
       <c r="R4" t="n">
-        <v>6619807</v>
+        <v>6619866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121108150</v>
+        <v>121107967</v>
       </c>
       <c r="B6" t="n">
-        <v>105203</v>
+        <v>8435</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,50 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687313</v>
+        <v>687303</v>
       </c>
       <c r="R6" t="n">
-        <v>6619866</v>
+        <v>6619820</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107967</v>
+        <v>121108047</v>
       </c>
       <c r="B7" t="n">
-        <v>8435</v>
+        <v>92024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,43 +1237,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687303</v>
+        <v>687309</v>
       </c>
       <c r="R7" t="n">
-        <v>6619820</v>
+        <v>6619846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107537</v>
+        <v>121107440</v>
       </c>
       <c r="B8" t="n">
-        <v>8435</v>
+        <v>79225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,47 +1339,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687377</v>
+        <v>687379</v>
       </c>
       <c r="R8" t="n">
-        <v>6619797</v>
+        <v>6619807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1431,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107965</v>
+        <v>121107537</v>
       </c>
       <c r="B9" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,43 +1441,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687312</v>
+        <v>687377</v>
       </c>
       <c r="R9" t="n">
-        <v>6619814</v>
+        <v>6619797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,6 +1522,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1538,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107620</v>
+        <v>121108045</v>
       </c>
       <c r="B10" t="n">
         <v>57370</v>
@@ -1572,24 +1575,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormossen, Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687383</v>
+        <v>687312</v>
       </c>
       <c r="R10" t="n">
-        <v>6619778</v>
+        <v>6619846</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
